--- a/diseases/d107/1995-1999.xlsx
+++ b/diseases/d107/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>3</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>3</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18988,9 +18850,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="S95" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19381,9 +19240,6 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="S97" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19919,9 +19775,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20312,9 +20165,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20850,9 +20700,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21243,9 +21090,6 @@
       <c r="O107" t="n">
         <v>2</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21781,9 +21625,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22174,9 +22015,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22712,9 +22550,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23105,9 +22940,6 @@
       <c r="O117" t="n">
         <v>4</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23643,9 +23475,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24036,9 +23865,6 @@
       <c r="O122" t="n">
         <v>2</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24574,9 +24400,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24967,9 +24790,6 @@
       <c r="O127" t="n">
         <v>2</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25505,9 +25325,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25898,9 +25715,6 @@
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26436,9 +26250,6 @@
       <c r="O135" t="n">
         <v>1</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26829,9 +26640,6 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27367,9 +27175,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27760,9 +27565,6 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28298,9 +28100,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28691,9 +28490,6 @@
       <c r="O147" t="n">
         <v>1</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="S147" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29229,9 +29025,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29622,9 +29415,6 @@
       <c r="O152" t="n">
         <v>1</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30160,9 +29950,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30553,9 +30340,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31091,9 +30875,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31484,9 +31265,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32022,9 +31800,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32415,9 +32190,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="S167" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32953,9 +32725,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33346,9 +33115,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33884,9 +33650,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="S175" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34277,9 +34040,6 @@
       <c r="O177" t="n">
         <v>1</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="S177" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34815,9 +34575,6 @@
       <c r="O180" t="n">
         <v>2</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35208,9 +34965,6 @@
       <c r="O182" t="n">
         <v>1</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35746,9 +35500,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="S185" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36139,9 +35890,6 @@
       <c r="O187" t="n">
         <v>2</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36677,9 +36425,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37070,9 +36815,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37608,9 +37350,6 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38001,9 +37740,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="S197" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38539,9 +38275,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38932,9 +38665,6 @@
       <c r="O202" t="n">
         <v>1</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39470,9 +39200,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39863,9 +39590,6 @@
       <c r="O207" t="n">
         <v>2</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40401,9 +40125,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40794,9 +40515,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41332,9 +41050,6 @@
       <c r="O215" t="n">
         <v>2</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41725,9 +41440,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="S217" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42118,9 +41830,6 @@
       <c r="O219" t="n">
         <v>0</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="S219" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42656,9 +42365,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43049,9 +42755,6 @@
       <c r="O224" t="n">
         <v>1</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43587,9 +43290,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43980,9 +43680,6 @@
       <c r="O229" t="n">
         <v>1</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44518,9 +44215,6 @@
       <c r="O232" t="n">
         <v>3</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44911,9 +44605,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45449,9 +45140,6 @@
       <c r="O237" t="n">
         <v>1</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45842,9 +45530,6 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="S239" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46380,9 +46065,6 @@
       <c r="O242" t="n">
         <v>3</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46773,9 +46455,6 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="S244" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47311,9 +46990,6 @@
       <c r="O247" t="n">
         <v>2</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="S247" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47704,9 +47380,6 @@
       <c r="O249" t="n">
         <v>1</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48242,9 +47915,6 @@
       <c r="O252" t="n">
         <v>1</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48635,9 +48305,6 @@
       <c r="O254" t="n">
         <v>0</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="S254" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49173,9 +48840,6 @@
       <c r="O257" t="n">
         <v>1</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49566,9 +49230,6 @@
       <c r="O259" t="n">
         <v>3</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="S259" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50104,9 +49765,6 @@
       <c r="O262" t="n">
         <v>1</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50497,9 +50155,6 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51035,9 +50690,6 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51428,9 +51080,6 @@
       <c r="O269" t="n">
         <v>1</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51964,9 +51613,6 @@
         <v>0</v>
       </c>
       <c r="O272" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q272" t="n">
         <v>0</v>
       </c>
       <c r="S272" t="inlineStr">
